--- a/engine/phar_study/EIPICO_Valuation_Model_10092026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_10092026.xlsx
@@ -2483,10 +2483,10 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>103.8007679145783</v>
+        <v>104.9105272908218</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>94.39540498598306</v>
+        <v>96.08964646722389</v>
       </c>
     </row>
     <row r="6">
@@ -2496,10 +2496,10 @@
         </is>
       </c>
       <c r="B6" s="16" t="n">
-        <v>120.563279729777</v>
+        <v>121.951229622625</v>
       </c>
       <c r="C6" s="16" t="n">
-        <v>118.416837770352</v>
+        <v>120.5086214711495</v>
       </c>
     </row>
     <row r="7">
@@ -2509,10 +2509,10 @@
         </is>
       </c>
       <c r="B7" s="16" t="n">
-        <v>131.6933256819726</v>
+        <v>132.7208728267296</v>
       </c>
       <c r="C7" s="16" t="n">
-        <v>135.3037034307837</v>
+        <v>136.8658343216828</v>
       </c>
     </row>
     <row r="8">
@@ -2522,10 +2522,10 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>143.9429398845258</v>
+        <v>144.4479983997303</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>154.3933534707429</v>
+        <v>155.4373533791256</v>
       </c>
     </row>
     <row r="9">
@@ -2535,10 +2535,10 @@
         </is>
       </c>
       <c r="B9" s="16" t="n">
-        <v>167.1694824698633</v>
+        <v>167.8488827718508</v>
       </c>
       <c r="C9" s="16" t="n">
-        <v>193.8196590270854</v>
+        <v>194.5986082406631</v>
       </c>
     </row>
     <row r="10">
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="B10" s="17" t="n">
-        <v>0.5380200000000001</v>
+        <v>0.56606</v>
       </c>
       <c r="C10" s="17" t="n">
-        <v>0.58168</v>
+        <v>0.60784</v>
       </c>
     </row>
     <row r="11">
@@ -2561,10 +2561,10 @@
         </is>
       </c>
       <c r="B11" s="17" t="n">
-        <v>0.26388</v>
+        <v>0.27418</v>
       </c>
       <c r="C11" s="17" t="n">
-        <v>0.38614</v>
+        <v>0.40504</v>
       </c>
     </row>
     <row r="12">
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="B12" s="17" t="n">
-        <v>0.1869</v>
+        <v>0.16364</v>
       </c>
       <c r="C12" s="17" t="n">
-        <v>0.23222</v>
+        <v>0.20604</v>
       </c>
     </row>
     <row r="13">
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="B13" s="17" t="n">
-        <v>0.43044</v>
+        <v>0.43642</v>
       </c>
       <c r="C13" s="17" t="n">
-        <v>0.63828</v>
+        <v>0.64934</v>
       </c>
     </row>
     <row r="14">
@@ -2600,10 +2600,10 @@
         </is>
       </c>
       <c r="B14" s="17" t="n">
-        <v>0.3294</v>
+        <v>0.29892</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>0.47868</v>
+        <v>0.4396</v>
       </c>
     </row>
     <row r="15">

--- a/engine/phar_study/EIPICO_Valuation_Model_10092026.xlsx
+++ b/engine/phar_study/EIPICO_Valuation_Model_10092026.xlsx
@@ -2780,19 +2780,19 @@
         </is>
       </c>
       <c r="B5" s="16" t="n">
-        <v>111.8970197888694</v>
+        <v>137.218415702402</v>
       </c>
       <c r="C5" s="16" t="n">
-        <v>97.27518652578942</v>
+        <v>117.2863789676158</v>
       </c>
       <c r="D5" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
       <c r="E5" s="16" t="n">
-        <v>75.18184914786232</v>
+        <v>88.48699928435364</v>
       </c>
       <c r="F5" s="16" t="n">
-        <v>66.64034543916641</v>
+        <v>77.75544103418943</v>
       </c>
     </row>
     <row r="7">
@@ -2824,19 +2824,19 @@
         </is>
       </c>
       <c r="B8" s="16" t="n">
-        <v>62.88157922448156</v>
+        <v>71.43540284280947</v>
       </c>
       <c r="C8" s="16" t="n">
-        <v>67.07295775526596</v>
+        <v>76.82996952584506</v>
       </c>
       <c r="D8" s="16" t="n">
-        <v>72.01935510321825</v>
+        <v>83.32559895438837</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>77.95987153831324</v>
+        <v>91.31758983325446</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
     </row>
     <row r="10">
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="B11" s="16" t="n">
-        <v>88.59403146910748</v>
+        <v>105.2656498456053</v>
       </c>
       <c r="C11" s="16" t="n">
-        <v>87.02663693440269</v>
+        <v>103.46319802436</v>
       </c>
       <c r="D11" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>83.97576515160245</v>
+        <v>99.95506171090351</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>81.75858809871139</v>
+        <v>97.40579890496625</v>
       </c>
     </row>
     <row r="13">
@@ -2912,19 +2912,19 @@
         </is>
       </c>
       <c r="B14" s="16" t="n">
-        <v>104.6939065410785</v>
+        <v>123.4188376710867</v>
       </c>
       <c r="C14" s="16" t="n">
-        <v>97.62211519256394</v>
+        <v>115.4178743727861</v>
       </c>
       <c r="D14" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
       <c r="E14" s="16" t="n">
-        <v>76.40674114702009</v>
+        <v>91.4149844778844</v>
       </c>
       <c r="F14" s="16" t="n">
-        <v>65.79905412424819</v>
+        <v>79.41353953043357</v>
       </c>
     </row>
     <row r="16">
@@ -2956,19 +2956,19 @@
         </is>
       </c>
       <c r="B17" s="16" t="n">
-        <v>98.2098508172061</v>
+        <v>115.7967598373575</v>
       </c>
       <c r="C17" s="16" t="n">
-        <v>91.72816557493466</v>
+        <v>108.6064742190587</v>
       </c>
       <c r="D17" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>78.76479509039191</v>
+        <v>94.22590298246129</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>72.28310984812053</v>
+        <v>87.0356173641626</v>
       </c>
     </row>
     <row r="19">
@@ -3000,19 +3000,19 @@
         </is>
       </c>
       <c r="B20" s="16" t="n">
-        <v>82.45938147348832</v>
+        <v>97.58338806202531</v>
       </c>
       <c r="C20" s="16" t="n">
-        <v>83.79246589461503</v>
+        <v>99.41927024524021</v>
       </c>
       <c r="D20" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
       <c r="E20" s="16" t="n">
-        <v>86.8286485079402</v>
+        <v>103.5837024163915</v>
       </c>
       <c r="F20" s="16" t="n">
-        <v>88.54647231967209</v>
+        <v>105.9317381678432</v>
       </c>
     </row>
     <row r="22">
@@ -3044,19 +3044,19 @@
         </is>
       </c>
       <c r="B23" s="16" t="n">
-        <v>90.58215156252788</v>
+        <v>107.7539611774374</v>
       </c>
       <c r="C23" s="16" t="n">
-        <v>87.37679410780088</v>
+        <v>103.9469366028464</v>
       </c>
       <c r="D23" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
       <c r="E23" s="16" t="n">
-        <v>82.92213412642026</v>
+        <v>98.65436965369446</v>
       </c>
       <c r="F23" s="16" t="n">
-        <v>80.1761478719565</v>
+        <v>95.39070577065706</v>
       </c>
     </row>
     <row r="25">
@@ -3088,19 +3088,19 @@
         </is>
       </c>
       <c r="B26" s="16" t="n">
-        <v>77.62715389634869</v>
+        <v>89.1491449442298</v>
       </c>
       <c r="C26" s="16" t="n">
-        <v>83.69626264945717</v>
+        <v>97.18833679086612</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>91.06014984352457</v>
+        <v>107.2053619892474</v>
       </c>
       <c r="E26" s="16" t="n">
-        <v>100.2053409468678</v>
+        <v>120.0643106351163</v>
       </c>
       <c r="F26" s="16" t="n">
-        <v>111.8970197888694</v>
+        <v>137.218415702402</v>
       </c>
     </row>
     <row r="27">
@@ -3110,19 +3110,19 @@
         </is>
       </c>
       <c r="B27" s="16" t="n">
-        <v>69.77120454458131</v>
+        <v>79.65393545907578</v>
       </c>
       <c r="C27" s="16" t="n">
-        <v>74.79304549706271</v>
+        <v>86.20402273902887</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>80.7968705152677</v>
+        <v>94.21694493473194</v>
       </c>
       <c r="E27" s="16" t="n">
-        <v>88.12018767938225</v>
+        <v>104.2692665851173</v>
       </c>
       <c r="F27" s="16" t="n">
-        <v>97.27518652578942</v>
+        <v>117.2863789676158</v>
       </c>
     </row>
     <row r="28">
@@ -3132,19 +3132,19 @@
         </is>
       </c>
       <c r="B28" s="16" t="n">
-        <v>62.88157922448156</v>
+        <v>71.43540284280947</v>
       </c>
       <c r="C28" s="16" t="n">
-        <v>67.07295775526596</v>
+        <v>76.82996952584506</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>72.01935510321825</v>
+        <v>83.32559895438837</v>
       </c>
       <c r="E28" s="16" t="n">
-        <v>77.95987153831324</v>
+        <v>91.31758983325446</v>
       </c>
       <c r="F28" s="16" t="n">
-        <v>85.24648033266337</v>
+        <v>101.4161886007601</v>
       </c>
     </row>
     <row r="29">
@@ -3154,19 +3154,19 @@
         </is>
       </c>
       <c r="B29" s="16" t="n">
-        <v>56.79406728633221</v>
+        <v>64.25686192632654</v>
       </c>
       <c r="C29" s="16" t="n">
-        <v>60.31883324517074</v>
+        <v>68.74118176830513</v>
       </c>
       <c r="D29" s="16" t="n">
-        <v>64.43094947944664</v>
+        <v>74.06664456978628</v>
       </c>
       <c r="E29" s="16" t="n">
-        <v>69.30286242568583</v>
+        <v>80.51052297507073</v>
       </c>
       <c r="F29" s="16" t="n">
-        <v>75.18184914786232</v>
+        <v>88.48699928435364</v>
       </c>
     </row>
     <row r="30">
@@ -3176,19 +3176,19 @@
         </is>
       </c>
       <c r="B30" s="16" t="n">
-        <v>51.3795256709253</v>
+        <v>57.9365521229984</v>
       </c>
       <c r="C30" s="16" t="n">
-        <v>54.3634422097047</v>
+        <v>61.69442643617823</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>57.80889741833875</v>
+        <v>66.10306166969437</v>
       </c>
       <c r="E30" s="16" t="n">
-        <v>61.8421940918188</v>
+        <v>71.3607476001043</v>
       </c>
       <c r="F30" s="16" t="n">
-        <v>66.64034543916641</v>
+        <v>77.75544103418943</v>
       </c>
     </row>
     <row r="32">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="B33" s="19" t="n">
-        <v>4238.94571426909</v>
+        <v>2215.661250634238</v>
       </c>
     </row>
     <row r="34">
@@ -3215,7 +3215,7 @@
         </is>
       </c>
       <c r="B34" s="17" t="n">
-        <v>0.1685442382213203</v>
+        <v>0.09580384248244556</v>
       </c>
     </row>
     <row r="35">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>60.45799355433216</v>
+        <v>31.60088442711414</v>
       </c>
     </row>
     <row r="36">
@@ -3235,7 +3235,7 @@
         </is>
       </c>
       <c r="B36" s="24" t="n">
-        <v>0.6045799355433216</v>
+        <v>0.3160088442711414</v>
       </c>
     </row>
   </sheetData>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 79% of core enterprise value, 68% of total</t>
+          <t>Terminal value 81% of core enterprise value, 71% of total</t>
         </is>
       </c>
     </row>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>Terminal value 78% of core enterprise value, 69% of total</t>
+          <t>Terminal value 81% of core enterprise value, 72% of total</t>
         </is>
       </c>
     </row>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Justified 1.92 times book</t>
+          <t>Justified 2.23 times book</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
         </is>
       </c>
       <c r="C56" s="21" t="n">
-        <v>0.105</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="57" ht="26" customHeight="1">
